--- a/artfynd/A 36749-2026 artfynd.xlsx
+++ b/artfynd/A 36749-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136348864</v>
       </c>
       <c r="B3" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36749-2026 artfynd.xlsx
+++ b/artfynd/A 36749-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136348864</v>
       </c>
       <c r="B3" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36749-2026 artfynd.xlsx
+++ b/artfynd/A 36749-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136348864</v>
       </c>
       <c r="B3" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
